--- a/public/exports-from-60/29189420.xlsx
+++ b/public/exports-from-60/29189420.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -24814,12 +24814,12 @@
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">310018566</t>
+          <t xml:space="preserve">310018578</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -27064,7 +27064,7 @@
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -27139,7 +27139,7 @@
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -27289,7 +27289,7 @@
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -27364,7 +27364,7 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -27439,12 +27439,12 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020300</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -27514,12 +27514,12 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020312</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -28039,7 +28039,7 @@
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
@@ -28114,7 +28114,7 @@
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -28189,7 +28189,7 @@
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -28264,7 +28264,7 @@
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -29314,7 +29314,7 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -29464,12 +29464,12 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020327</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020292</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M394" t="inlineStr">
@@ -29614,7 +29614,7 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -30214,7 +30214,7 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
@@ -30289,7 +30289,7 @@
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020316</t>
+          <t xml:space="preserve">310020329</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
@@ -33964,12 +33964,12 @@
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M453" t="inlineStr">
@@ -34039,12 +34039,12 @@
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M454" t="inlineStr">
@@ -34114,12 +34114,12 @@
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M455" t="inlineStr">
@@ -34189,12 +34189,12 @@
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M456" t="inlineStr">
@@ -34264,12 +34264,12 @@
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M457" t="inlineStr">
@@ -34339,12 +34339,12 @@
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M458" t="inlineStr">
@@ -34414,12 +34414,12 @@
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M459" t="inlineStr">
@@ -34489,12 +34489,12 @@
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M460" t="inlineStr">
@@ -34564,12 +34564,12 @@
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M461" t="inlineStr">
@@ -34639,12 +34639,12 @@
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M462" t="inlineStr">
@@ -34714,12 +34714,12 @@
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M463" t="inlineStr">
@@ -34789,12 +34789,12 @@
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M464" t="inlineStr">
@@ -34864,12 +34864,12 @@
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M465" t="inlineStr">
@@ -34939,12 +34939,12 @@
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M466" t="inlineStr">
@@ -35014,12 +35014,12 @@
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M467" t="inlineStr">
@@ -35089,12 +35089,12 @@
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M468" t="inlineStr">
@@ -35164,12 +35164,12 @@
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M469" t="inlineStr">
@@ -35239,12 +35239,12 @@
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M470" t="inlineStr">
@@ -35314,12 +35314,12 @@
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M471" t="inlineStr">
@@ -35389,12 +35389,12 @@
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M472" t="inlineStr">
@@ -35464,12 +35464,12 @@
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M473" t="inlineStr">
@@ -35539,12 +35539,12 @@
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M474" t="inlineStr">
@@ -35614,12 +35614,12 @@
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M475" t="inlineStr">
@@ -35689,12 +35689,12 @@
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M476" t="inlineStr">
@@ -35764,12 +35764,12 @@
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028677</t>
+          <t xml:space="preserve">310028681</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M477" t="inlineStr">
@@ -48439,7 +48439,7 @@
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477935</t>
+          <t xml:space="preserve">311477990</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
@@ -58639,7 +58639,7 @@
       </c>
       <c r="K782" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555497</t>
+          <t xml:space="preserve">311555498</t>
         </is>
       </c>
       <c r="L782" t="inlineStr">
@@ -62464,7 +62464,7 @@
       </c>
       <c r="K833" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568868</t>
+          <t xml:space="preserve">311568869</t>
         </is>
       </c>
       <c r="L833" t="inlineStr">
@@ -62839,7 +62839,7 @@
       </c>
       <c r="K838" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568866</t>
+          <t xml:space="preserve">311568869</t>
         </is>
       </c>
       <c r="L838" t="inlineStr">
@@ -67714,12 +67714,12 @@
       </c>
       <c r="K903" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803905</t>
+          <t xml:space="preserve">311803934</t>
         </is>
       </c>
       <c r="L903" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M903" t="inlineStr">

--- a/public/exports-from-60/29189420.xlsx
+++ b/public/exports-from-60/29189420.xlsx
@@ -25114,12 +25114,12 @@
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t xml:space="preserve">310018603</t>
+          <t xml:space="preserve">310018611</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -33964,12 +33964,12 @@
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M453" t="inlineStr">
@@ -34039,12 +34039,12 @@
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M454" t="inlineStr">
@@ -34114,12 +34114,12 @@
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M455" t="inlineStr">
@@ -34189,12 +34189,12 @@
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M456" t="inlineStr">
@@ -34264,12 +34264,12 @@
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M457" t="inlineStr">
@@ -34339,12 +34339,12 @@
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M458" t="inlineStr">
@@ -34414,12 +34414,12 @@
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M459" t="inlineStr">
@@ -34489,12 +34489,12 @@
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
@@ -34564,12 +34564,12 @@
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M461" t="inlineStr">
@@ -34639,12 +34639,12 @@
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M462" t="inlineStr">
@@ -34714,12 +34714,12 @@
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M463" t="inlineStr">
@@ -34789,12 +34789,12 @@
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M464" t="inlineStr">
@@ -34864,12 +34864,12 @@
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M465" t="inlineStr">
@@ -34939,12 +34939,12 @@
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M466" t="inlineStr">
@@ -35014,12 +35014,12 @@
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M467" t="inlineStr">
@@ -35089,12 +35089,12 @@
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M468" t="inlineStr">
@@ -35164,12 +35164,12 @@
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M469" t="inlineStr">
@@ -35239,12 +35239,12 @@
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
@@ -35314,12 +35314,12 @@
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M471" t="inlineStr">
@@ -35389,12 +35389,12 @@
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M472" t="inlineStr">
@@ -35464,12 +35464,12 @@
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M473" t="inlineStr">
@@ -35539,12 +35539,12 @@
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M474" t="inlineStr">
@@ -35614,12 +35614,12 @@
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M475" t="inlineStr">
@@ -35689,12 +35689,12 @@
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M476" t="inlineStr">
@@ -35764,12 +35764,12 @@
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t xml:space="preserve">310028681</t>
+          <t xml:space="preserve">310028677</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M477" t="inlineStr">
@@ -48439,7 +48439,7 @@
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t xml:space="preserve">311477990</t>
+          <t xml:space="preserve">311477935</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
@@ -58639,7 +58639,7 @@
       </c>
       <c r="K782" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555498</t>
+          <t xml:space="preserve">311555497</t>
         </is>
       </c>
       <c r="L782" t="inlineStr">
@@ -62239,7 +62239,7 @@
       </c>
       <c r="K830" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568269</t>
+          <t xml:space="preserve">311568275</t>
         </is>
       </c>
       <c r="L830" t="inlineStr">
@@ -62914,7 +62914,7 @@
       </c>
       <c r="K839" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568867</t>
+          <t xml:space="preserve">311568869</t>
         </is>
       </c>
       <c r="L839" t="inlineStr">
@@ -67714,12 +67714,12 @@
       </c>
       <c r="K903" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803934</t>
+          <t xml:space="preserve">311803905</t>
         </is>
       </c>
       <c r="L903" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M903" t="inlineStr">
